--- a/output/pdf_financials_xlsx/DXT.xlsx
+++ b/output/pdf_financials_xlsx/DXT.xlsx
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-3.9e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-8.500000000000001e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-3.9e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.0965</v>
+        <v>-0.09646100000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.00779</v>
+        <v>0.007875</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.023872</v>
+        <v>0.023911</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.087533</v>
+        <v>-0.087494</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.016659</v>
+        <v>0.016744</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.04905</v>
+        <v>0.049089</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-48.41989390360606</v>
+        <v>-48.39832060139729</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11.11793324835323</v>
+        <v>11.17466080259478</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>20.50088189318643</v>
+        <v>20.51718228857552</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -63920,7 +63920,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -66383,7 +66383,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -69264,7 +69264,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -71477,7 +71477,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -74568,7 +74568,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E659" s="5" t="n">

--- a/output/pdf_financials_xlsx/DXT.xlsx
+++ b/output/pdf_financials_xlsx/DXT.xlsx
@@ -2111,40 +2111,40 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.008966999999999999</v>
+        <v>0.023282</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.008869</v>
+        <v>0.025917</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.025178</v>
+        <v>0.008533000000000001</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.029723</v>
+        <v>0.008303</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.040211</v>
+        <v>0.008203999999999999</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.054683</v>
+        <v>0.00706</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.056895</v>
+        <v>0.002968</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.053964</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.04984</v>
+        <v>0.000992</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.043443</v>
+        <v>0.002742</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.041289</v>
+        <v>0.002749</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.047206</v>
+        <v>0.002913</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.038605</v>
+        <v>0.005513</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.034975</v>
+        <v>0.004895</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.035205</v>
+        <v>0.005363</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.042343</v>
+        <v>0.005415</v>
       </c>
     </row>
     <row r="29">
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.087494</v>
+        <v>-0.07317899999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.016744</v>
+        <v>0.033792</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.049089</v>
+        <v>0.032444</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2203,16 +2203,16 @@
         <v>0.055598</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.029524</v>
+        <v>-0.019324</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.0356</v>
+        <v>-0.005101</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.033093</v>
+        <v>-0.005447</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.03758</v>
+        <v>-0.081873</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.041825</v>
+        <v>0.008732999999999999</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.082479</v>
+        <v>0.052399</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.088842</v>
+        <v>0.059</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.09703199999999999</v>
+        <v>0.060104</v>
       </c>
     </row>
     <row r="30">
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-48.39832060139729</v>
+        <v>-40.47981236758694</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11.17466080259478</v>
+        <v>22.552206034477</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>20.51718228857552</v>
+        <v>13.56025712828829</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2271,16 +2271,16 @@
         <v>15.03099578522205</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.76559666845996</v>
+        <v>-7.700799011696256</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>10.98487419850532</v>
+        <v>-1.573984361982461</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>8.394018947608721</v>
+        <v>-1.381628175373182</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-8.203520659425099</v>
+        <v>-17.87245468198805</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2288,16 +2288,16 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>4.305122813085103</v>
+        <v>0.8989034674637705</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>8.88996913047977</v>
+        <v>5.647807229331217</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>8.857388684452165</v>
+        <v>5.882194596955017</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>9.318799519807923</v>
+        <v>5.772292917166866</v>
       </c>
     </row>
     <row r="31">
@@ -6551,40 +6551,40 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.023282</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.025917</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.008533000000000001</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.008303</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.008203999999999999</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.00706</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.002968</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.000992</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.002742</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.002749</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.002913</v>
       </c>
       <c r="N100" s="1" t="inlineStr">
         <is>
@@ -6592,18 +6592,16 @@
         </is>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.005513</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.004895</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005363</v>
+      </c>
+      <c r="R100" s="3" t="n">
+        <v>0.005415</v>
       </c>
     </row>
     <row r="101">
@@ -7316,13 +7314,13 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.01324</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.007993999999999999</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.000885</v>
       </c>
       <c r="N112" s="1" t="inlineStr">
         <is>
@@ -8198,18 +8196,16 @@
         </is>
       </c>
       <c r="O126" s="3" t="n">
-        <v>0</v>
+        <v>-0.000815</v>
       </c>
       <c r="P126" s="3" t="n">
-        <v>0</v>
+        <v>-0.000331</v>
       </c>
       <c r="Q126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R126" s="3" t="n">
+        <v>-0.000325</v>
       </c>
     </row>
     <row r="127">
@@ -34276,7 +34272,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -36988,7 +36984,11 @@
           <t>Dividends paid to non-controlling interest</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -39287,7 +39287,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -41913,7 +41913,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -43792,7 +43792,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -44895,7 +44899,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -46574,7 +46578,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -49239,7 +49243,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -52092,7 +52096,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E433" s="5" t="n">
         <v>0.014315</v>
       </c>
@@ -52191,7 +52199,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E434" s="5" t="n">
@@ -56506,7 +56514,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -59813,7 +59821,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -61637,7 +61645,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -64611,7 +64619,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -66779,7 +66787,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -70030,7 +70038,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
@@ -72055,7 +72063,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -73964,7 +73972,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E653" s="5" t="n">
         <v>0.014315</v>
       </c>
@@ -74063,7 +74075,7 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E654" s="5" t="n">
